--- a/artfynd/A 55925-2025 artfynd.xlsx
+++ b/artfynd/A 55925-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83629213</v>
+        <v>16535349</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Flikros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Rosa tomentella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Léman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +708,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Garnanäs, NV Almesvik, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505791.5235097955</v>
+        <v>505787</v>
       </c>
       <c r="R2" t="n">
-        <v>6223270.846111638</v>
+        <v>6223237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,34 +752,14 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>31D61403-74F1-4D8D-A1FA-1A9EEF644313</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspetthål</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,77 +770,83 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>bryn</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Åke Widgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Jörgen Dahlin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83629901</v>
+        <v>98326028</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>101246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>6223427, 505701, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505827.8389454451</v>
+        <v>505701</v>
       </c>
       <c r="R3" t="n">
-        <v>6223238.597336248</v>
+        <v>6223427</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,29 +868,19 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>19E1361E-24F0-4EDB-BD5B-B2FC1ABAF844</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,53 +895,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Isabel Rodeson</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83629210</v>
+        <v>98336776</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>101246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,19 +944,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>6223456, 505724, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505876.1956717306</v>
+        <v>505724</v>
       </c>
       <c r="R4" t="n">
-        <v>6223378.43404586</v>
+        <v>6223456</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,29 +988,19 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>13CEA02C-1906-495C-B2C8-E27547D2E8DC</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,31 +1015,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Jörgen Dahlin</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83629246</v>
+        <v>83629210</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505748.3234039299</v>
+        <v>505876</v>
       </c>
       <c r="R5" t="n">
-        <v>6223443.967954644</v>
+        <v>6223378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1100,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>AB33171E-3875-4AC6-AEEF-446E410EA77C</t>
+          <t>13CEA02C-1906-495C-B2C8-E27547D2E8DC</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1137,19 +1108,9 @@
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,15 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83629261</v>
+        <v>83629213</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505646.945582687</v>
+        <v>505792</v>
       </c>
       <c r="R6" t="n">
-        <v>6223308.519476001</v>
+        <v>6223271</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,7 +1210,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>68C90E01-8699-4CFE-94AD-097A2795D966</t>
+          <t>31D61403-74F1-4D8D-A1FA-1A9EEF644313</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1262,19 +1218,14 @@
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspetthål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,15 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83629249</v>
+        <v>83629231</v>
       </c>
       <c r="B7" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505740.5486922004</v>
+        <v>505625</v>
       </c>
       <c r="R7" t="n">
-        <v>6223416.115557197</v>
+        <v>6223301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1325,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>8DC83E03-445D-4FC1-9596-F2F22E5FF6AB</t>
+          <t>49D70BFB-6C0D-46F0-B2DC-BC4984058084</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1387,19 +1333,9 @@
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,53 +1366,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83829108</v>
+        <v>83629245</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spillkråka (Skyddsvärt träd), Bl</t>
+          <t>Ask (Skyddsvärt träd), Bl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505773.6780190495</v>
+        <v>505751</v>
       </c>
       <c r="R8" t="n">
-        <v>6223262.4691212</v>
+        <v>6223457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,7 +1435,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>90B7FDE8-68A1-4ACD-8AF7-EB9DB0883ED8</t>
+          <t>CB3F6D1B-B14A-4224-AA99-226E0F44B6F3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1511,23 +1443,13 @@
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
@@ -1543,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1554,15 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83629247</v>
+        <v>83629246</v>
       </c>
       <c r="B9" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505752.2406213371</v>
+        <v>505748</v>
       </c>
       <c r="R9" t="n">
-        <v>6223435.620637672</v>
+        <v>6223444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,7 +1545,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>452B07C7-CA47-41A1-80C3-BC3208469AD6</t>
+          <t>AB33171E-3875-4AC6-AEEF-446E410EA77C</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1636,19 +1553,9 @@
           <t>2012-12-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,37 +1586,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16535349</v>
+        <v>83629247</v>
       </c>
       <c r="B10" t="n">
-        <v>100152</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1400</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flikros</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rosa tomentella</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Léman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1717,26 +1619,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Garnanäs, NV Almesvik, Bl</t>
+          <t>Ask (Skyddsvärt träd), Bl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505787.1044438274</v>
+        <v>505752</v>
       </c>
       <c r="R10" t="n">
-        <v>6223237.428404811</v>
+        <v>6223436</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,24 +1653,19 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>452B07C7-CA47-41A1-80C3-BC3208469AD6</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,88 +1676,72 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>bryn</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Åke Widgren</t>
+          <t>Johan Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åke Widgren</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98326028</v>
+        <v>83629249</v>
       </c>
       <c r="B11" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101246</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6223427, 505701, Bl</t>
+          <t>Ask (Skyddsvärt träd), Bl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505700.915566848</v>
+        <v>505741</v>
       </c>
       <c r="R11" t="n">
-        <v>6223427.199457482</v>
+        <v>6223416</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1892,29 +1763,19 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8DC83E03-445D-4FC1-9596-F2F22E5FF6AB</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ekoxeuppropet 2020.</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,17 +1790,677 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Johan Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Monika Sunhede</t>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Ekoxeuppropet 2020</t>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>83629261</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>505647</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6223309</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>68C90E01-8699-4CFE-94AD-097A2795D966</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>83629263</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505620</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6223470</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>ECB5A90C-4418-4FE9-B0DC-DE1226807B54</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>83629264</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>505623</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6223472</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2CABF23C-EEFF-4A80-B1B9-CE7061317544</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>83629265</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>505610</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6223462</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>CF7D251A-0AD0-4071-8ACC-83B7375ED2B2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>83629266</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>505610</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6223468</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2FF72488-D3EF-4EF1-AF45-CE1E2636F5CF</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2012-12-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>83629901</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>505828</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6223239</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>19E1361E-24F0-4EDB-BD5B-B2FC1ABAF844</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Isabel Rodeson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 55925-2025 artfynd.xlsx
+++ b/artfynd/A 55925-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,32 +1051,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83629210</v>
+        <v>136039736</v>
       </c>
       <c r="B5" t="n">
-        <v>106813</v>
+        <v>9417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>101246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1086,17 +1086,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Biskopsmålavägen 21, Bl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505876</v>
+        <v>505720</v>
       </c>
       <c r="R5" t="n">
-        <v>6223378</v>
+        <v>6223438</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,19 +1118,29 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>13CEA02C-1906-495C-B2C8-E27547D2E8DC</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hona</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,28 +1155,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Jörgen Dahlin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629210</t>
+          <t>https://artportalen.se/Sighting/136039736</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83629213</v>
+        <v>83629210</v>
       </c>
       <c r="B6" t="n">
         <v>106813</v>
@@ -1205,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505792</v>
+        <v>505876</v>
       </c>
       <c r="R6" t="n">
-        <v>6223271</v>
+        <v>6223378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>31D61403-74F1-4D8D-A1FA-1A9EEF644313</t>
+          <t>13CEA02C-1906-495C-B2C8-E27547D2E8DC</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1246,11 +1252,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackspetthål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,13 +1281,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629213</t>
+          <t>https://artportalen.se/Sighting/83629210</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83629231</v>
+        <v>83629213</v>
       </c>
       <c r="B7" t="n">
         <v>106813</v>
@@ -1325,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505625</v>
+        <v>505792</v>
       </c>
       <c r="R7" t="n">
-        <v>6223301</v>
+        <v>6223271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1356,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>49D70BFB-6C0D-46F0-B2DC-BC4984058084</t>
+          <t>31D61403-74F1-4D8D-A1FA-1A9EEF644313</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1366,6 +1367,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspetthål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,13 +1401,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629231</t>
+          <t>https://artportalen.se/Sighting/83629213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83629245</v>
+        <v>83629231</v>
       </c>
       <c r="B8" t="n">
         <v>106813</v>
@@ -1440,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505751</v>
+        <v>505625</v>
       </c>
       <c r="R8" t="n">
-        <v>6223457</v>
+        <v>6223301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1476,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CB3F6D1B-B14A-4224-AA99-226E0F44B6F3</t>
+          <t>49D70BFB-6C0D-46F0-B2DC-BC4984058084</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1510,13 +1516,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629245</t>
+          <t>https://artportalen.se/Sighting/83629231</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83629246</v>
+        <v>83629245</v>
       </c>
       <c r="B9" t="n">
         <v>106813</v>
@@ -1555,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505748</v>
+        <v>505751</v>
       </c>
       <c r="R9" t="n">
-        <v>6223444</v>
+        <v>6223457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1591,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>AB33171E-3875-4AC6-AEEF-446E410EA77C</t>
+          <t>CB3F6D1B-B14A-4224-AA99-226E0F44B6F3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1625,13 +1631,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629246</t>
+          <t>https://artportalen.se/Sighting/83629245</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83629247</v>
+        <v>83629246</v>
       </c>
       <c r="B10" t="n">
         <v>106813</v>
@@ -1670,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505752</v>
+        <v>505748</v>
       </c>
       <c r="R10" t="n">
-        <v>6223436</v>
+        <v>6223444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1706,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>452B07C7-CA47-41A1-80C3-BC3208469AD6</t>
+          <t>AB33171E-3875-4AC6-AEEF-446E410EA77C</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1740,13 +1746,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629247</t>
+          <t>https://artportalen.se/Sighting/83629246</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>83629249</v>
+        <v>83629247</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1785,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505741</v>
+        <v>505752</v>
       </c>
       <c r="R11" t="n">
-        <v>6223416</v>
+        <v>6223436</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1821,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>8DC83E03-445D-4FC1-9596-F2F22E5FF6AB</t>
+          <t>452B07C7-CA47-41A1-80C3-BC3208469AD6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1855,13 +1861,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629249</t>
+          <t>https://artportalen.se/Sighting/83629247</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>83629261</v>
+        <v>83629249</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1900,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505647</v>
+        <v>505741</v>
       </c>
       <c r="R12" t="n">
-        <v>6223309</v>
+        <v>6223416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1936,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>68C90E01-8699-4CFE-94AD-097A2795D966</t>
+          <t>8DC83E03-445D-4FC1-9596-F2F22E5FF6AB</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1970,13 +1976,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629261</t>
+          <t>https://artportalen.se/Sighting/83629249</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83629263</v>
+        <v>83629261</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2015,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505620</v>
+        <v>505647</v>
       </c>
       <c r="R13" t="n">
-        <v>6223470</v>
+        <v>6223309</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,17 +2051,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>ECB5A90C-4418-4FE9-B0DC-DE1226807B54</t>
+          <t>68C90E01-8699-4CFE-94AD-097A2795D966</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-12-12</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-12-12</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,13 +2091,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629263</t>
+          <t>https://artportalen.se/Sighting/83629261</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83629264</v>
+        <v>83629263</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2130,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505623</v>
+        <v>505620</v>
       </c>
       <c r="R14" t="n">
-        <v>6223472</v>
+        <v>6223470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2166,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2CABF23C-EEFF-4A80-B1B9-CE7061317544</t>
+          <t>ECB5A90C-4418-4FE9-B0DC-DE1226807B54</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2200,13 +2206,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629264</t>
+          <t>https://artportalen.se/Sighting/83629263</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>83629265</v>
+        <v>83629264</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2245,10 +2251,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505610</v>
+        <v>505623</v>
       </c>
       <c r="R15" t="n">
-        <v>6223462</v>
+        <v>6223472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2281,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>CF7D251A-0AD0-4071-8ACC-83B7375ED2B2</t>
+          <t>2CABF23C-EEFF-4A80-B1B9-CE7061317544</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2315,13 +2321,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629265</t>
+          <t>https://artportalen.se/Sighting/83629264</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>83629266</v>
+        <v>83629265</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2363,7 +2369,7 @@
         <v>505610</v>
       </c>
       <c r="R16" t="n">
-        <v>6223468</v>
+        <v>6223462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2396,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2FF72488-D3EF-4EF1-AF45-CE1E2636F5CF</t>
+          <t>CF7D251A-0AD0-4071-8ACC-83B7375ED2B2</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2430,13 +2436,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629266</t>
+          <t>https://artportalen.se/Sighting/83629265</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>83629901</v>
+        <v>83629266</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2475,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505828</v>
+        <v>505610</v>
       </c>
       <c r="R17" t="n">
-        <v>6223239</v>
+        <v>6223468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,17 +2511,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>19E1361E-24F0-4EDB-BD5B-B2FC1ABAF844</t>
+          <t>2FF72488-D3EF-4EF1-AF45-CE1E2636F5CF</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2012-12-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2012-12-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,15 +2541,130 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83629266</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>83629901</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>505828</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6223239</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>19E1361E-24F0-4EDB-BD5B-B2FC1ABAF844</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
           <t>Johan Karlsson, Isabel Rodeson</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83629901</t>
         </is>
@@ -2567,6 +2688,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55925-2025 artfynd.xlsx
+++ b/artfynd/A 55925-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,32 +1172,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83629210</v>
+        <v>136501668</v>
       </c>
       <c r="B6" t="n">
-        <v>106813</v>
+        <v>9417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>101246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Biskopsmålavägen 21, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505876</v>
+        <v>505720</v>
       </c>
       <c r="R6" t="n">
-        <v>6223378</v>
+        <v>6223458</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,19 +1239,29 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>13CEA02C-1906-495C-B2C8-E27547D2E8DC</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,28 +1276,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Jörgen Dahlin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629210</t>
+          <t>https://artportalen.se/Sighting/136501668</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83629213</v>
+        <v>83629210</v>
       </c>
       <c r="B7" t="n">
         <v>106813</v>
@@ -1326,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505792</v>
+        <v>505876</v>
       </c>
       <c r="R7" t="n">
-        <v>6223271</v>
+        <v>6223378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1362,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>31D61403-74F1-4D8D-A1FA-1A9EEF644313</t>
+          <t>13CEA02C-1906-495C-B2C8-E27547D2E8DC</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1367,11 +1373,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-12-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspetthål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,13 +1402,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629213</t>
+          <t>https://artportalen.se/Sighting/83629210</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83629231</v>
+        <v>83629213</v>
       </c>
       <c r="B8" t="n">
         <v>106813</v>
@@ -1446,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505625</v>
+        <v>505792</v>
       </c>
       <c r="R8" t="n">
-        <v>6223301</v>
+        <v>6223271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1477,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>49D70BFB-6C0D-46F0-B2DC-BC4984058084</t>
+          <t>31D61403-74F1-4D8D-A1FA-1A9EEF644313</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1487,6 +1488,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspetthål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,13 +1522,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629231</t>
+          <t>https://artportalen.se/Sighting/83629213</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83629245</v>
+        <v>83629231</v>
       </c>
       <c r="B9" t="n">
         <v>106813</v>
@@ -1561,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505751</v>
+        <v>505625</v>
       </c>
       <c r="R9" t="n">
-        <v>6223457</v>
+        <v>6223301</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1597,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>CB3F6D1B-B14A-4224-AA99-226E0F44B6F3</t>
+          <t>49D70BFB-6C0D-46F0-B2DC-BC4984058084</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1631,13 +1637,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629245</t>
+          <t>https://artportalen.se/Sighting/83629231</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83629246</v>
+        <v>83629245</v>
       </c>
       <c r="B10" t="n">
         <v>106813</v>
@@ -1676,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505748</v>
+        <v>505751</v>
       </c>
       <c r="R10" t="n">
-        <v>6223444</v>
+        <v>6223457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1712,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>AB33171E-3875-4AC6-AEEF-446E410EA77C</t>
+          <t>CB3F6D1B-B14A-4224-AA99-226E0F44B6F3</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1746,13 +1752,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629246</t>
+          <t>https://artportalen.se/Sighting/83629245</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>83629247</v>
+        <v>83629246</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1791,10 +1797,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505752</v>
+        <v>505748</v>
       </c>
       <c r="R11" t="n">
-        <v>6223436</v>
+        <v>6223444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1827,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>452B07C7-CA47-41A1-80C3-BC3208469AD6</t>
+          <t>AB33171E-3875-4AC6-AEEF-446E410EA77C</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1861,13 +1867,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629247</t>
+          <t>https://artportalen.se/Sighting/83629246</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>83629249</v>
+        <v>83629247</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1906,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505741</v>
+        <v>505752</v>
       </c>
       <c r="R12" t="n">
-        <v>6223416</v>
+        <v>6223436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1942,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>8DC83E03-445D-4FC1-9596-F2F22E5FF6AB</t>
+          <t>452B07C7-CA47-41A1-80C3-BC3208469AD6</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1976,13 +1982,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629249</t>
+          <t>https://artportalen.se/Sighting/83629247</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83629261</v>
+        <v>83629249</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2021,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505647</v>
+        <v>505741</v>
       </c>
       <c r="R13" t="n">
-        <v>6223309</v>
+        <v>6223416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,7 +2057,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>68C90E01-8699-4CFE-94AD-097A2795D966</t>
+          <t>8DC83E03-445D-4FC1-9596-F2F22E5FF6AB</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2091,13 +2097,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629261</t>
+          <t>https://artportalen.se/Sighting/83629249</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83629263</v>
+        <v>83629261</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2136,10 +2142,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505620</v>
+        <v>505647</v>
       </c>
       <c r="R14" t="n">
-        <v>6223470</v>
+        <v>6223309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,17 +2172,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>ECB5A90C-4418-4FE9-B0DC-DE1226807B54</t>
+          <t>68C90E01-8699-4CFE-94AD-097A2795D966</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-12-12</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-12-12</t>
+          <t>2012-12-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,13 +2212,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629263</t>
+          <t>https://artportalen.se/Sighting/83629261</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>83629264</v>
+        <v>83629263</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2251,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505623</v>
+        <v>505620</v>
       </c>
       <c r="R15" t="n">
-        <v>6223472</v>
+        <v>6223470</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2281,7 +2287,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2CABF23C-EEFF-4A80-B1B9-CE7061317544</t>
+          <t>ECB5A90C-4418-4FE9-B0DC-DE1226807B54</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2321,13 +2327,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629264</t>
+          <t>https://artportalen.se/Sighting/83629263</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>83629265</v>
+        <v>83629264</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2366,10 +2372,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505610</v>
+        <v>505623</v>
       </c>
       <c r="R16" t="n">
-        <v>6223462</v>
+        <v>6223472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2402,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CF7D251A-0AD0-4071-8ACC-83B7375ED2B2</t>
+          <t>2CABF23C-EEFF-4A80-B1B9-CE7061317544</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2436,13 +2442,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629265</t>
+          <t>https://artportalen.se/Sighting/83629264</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>83629266</v>
+        <v>83629265</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2484,7 +2490,7 @@
         <v>505610</v>
       </c>
       <c r="R17" t="n">
-        <v>6223468</v>
+        <v>6223462</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,7 +2517,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2FF72488-D3EF-4EF1-AF45-CE1E2636F5CF</t>
+          <t>CF7D251A-0AD0-4071-8ACC-83B7375ED2B2</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2551,13 +2557,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83629266</t>
+          <t>https://artportalen.se/Sighting/83629265</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>83629901</v>
+        <v>83629266</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2596,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505828</v>
+        <v>505610</v>
       </c>
       <c r="R18" t="n">
-        <v>6223239</v>
+        <v>6223468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,17 +2632,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>19E1361E-24F0-4EDB-BD5B-B2FC1ABAF844</t>
+          <t>2FF72488-D3EF-4EF1-AF45-CE1E2636F5CF</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2012-12-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2012-12-07</t>
+          <t>2012-12-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,15 +2662,130 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
+          <t>Johan Karlsson, Jörgen Dahlin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83629266</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>83629901</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>505828</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6223239</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>19E1361E-24F0-4EDB-BD5B-B2FC1ABAF844</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2012-12-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
           <t>Johan Karlsson, Isabel Rodeson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83629901</t>
         </is>
@@ -2689,6 +2810,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
